--- a/data/participants_megtusalen.xlsx
+++ b/data/participants_megtusalen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cristina\repos\megtusalen_validation2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF616C0D-95D5-4446-8893-51CDFAA6682F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724670F9-6DD4-4064-A8E3-301DF8DD4F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29895" yWindow="3105" windowWidth="21600" windowHeight="11295" xr2:uid="{A8CE7551-8922-47F6-B549-E6B85DA15C6C}"/>
+    <workbookView xWindow="30225" yWindow="2820" windowWidth="21600" windowHeight="13725" xr2:uid="{A8CE7551-8922-47F6-B549-E6B85DA15C6C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$BO$730</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10920" uniqueCount="1578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8731" uniqueCount="1578">
   <si>
     <t>umeccd010</t>
   </si>
@@ -81080,39 +81080,6 @@
       <c r="AY496">
         <v>24</v>
       </c>
-      <c r="BA496">
-        <v>33</v>
-      </c>
-      <c r="BB496" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC496" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD496" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE496" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF496" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG496" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH496" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI496" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ496" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK496" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL496">
         <v>1</v>
       </c>
@@ -81235,39 +81202,6 @@
       <c r="AY497">
         <v>20</v>
       </c>
-      <c r="BA497">
-        <v>44</v>
-      </c>
-      <c r="BB497" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC497" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD497" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE497" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF497" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG497" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH497" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI497" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ497" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK497" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL497">
         <v>1</v>
       </c>
@@ -81390,39 +81324,6 @@
       <c r="AY498">
         <v>23</v>
       </c>
-      <c r="BA498">
-        <v>33</v>
-      </c>
-      <c r="BB498" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC498" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD498" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE498" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF498" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG498" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH498" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI498" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ498" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK498" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL498">
         <v>1</v>
       </c>
@@ -81551,39 +81452,6 @@
       <c r="AY499">
         <v>24</v>
       </c>
-      <c r="BA499">
-        <v>33</v>
-      </c>
-      <c r="BB499" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC499" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD499" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE499" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF499" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG499" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH499" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI499" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ499" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK499" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL499">
         <v>1</v>
       </c>
@@ -81712,39 +81580,6 @@
       <c r="AY500">
         <v>22</v>
       </c>
-      <c r="BA500">
-        <v>34</v>
-      </c>
-      <c r="BB500" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC500" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD500" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE500" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF500" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG500" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH500" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI500" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ500" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK500" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL500">
         <v>1</v>
       </c>
@@ -81873,39 +81708,6 @@
       <c r="AY501">
         <v>23</v>
       </c>
-      <c r="BA501">
-        <v>34</v>
-      </c>
-      <c r="BB501" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC501" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD501" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE501" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF501" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG501" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH501" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI501" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ501" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK501" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL501">
         <v>0</v>
       </c>
@@ -82034,39 +81836,6 @@
       <c r="AY502">
         <v>24</v>
       </c>
-      <c r="BA502">
-        <v>34</v>
-      </c>
-      <c r="BB502" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC502" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD502" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE502" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF502" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG502" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH502" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI502" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ502" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK502" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL502">
         <v>1</v>
       </c>
@@ -82195,39 +81964,6 @@
       <c r="AY503">
         <v>24</v>
       </c>
-      <c r="BA503">
-        <v>33</v>
-      </c>
-      <c r="BB503" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC503" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD503" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE503" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF503" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG503" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH503" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI503" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ503" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK503" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL503">
         <v>1</v>
       </c>
@@ -82356,39 +82092,6 @@
       <c r="AY504">
         <v>24</v>
       </c>
-      <c r="BA504">
-        <v>33</v>
-      </c>
-      <c r="BB504" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC504" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD504" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE504" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF504" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG504" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH504" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI504" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BJ504" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK504" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL504">
         <v>1</v>
       </c>
@@ -82517,39 +82220,6 @@
       <c r="AY505">
         <v>24</v>
       </c>
-      <c r="BA505">
-        <v>33</v>
-      </c>
-      <c r="BB505" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC505" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD505" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE505" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF505" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG505" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH505" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI505" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ505" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK505" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL505">
         <v>1</v>
       </c>
@@ -82678,39 +82348,6 @@
       <c r="AY506">
         <v>24</v>
       </c>
-      <c r="BA506">
-        <v>33</v>
-      </c>
-      <c r="BB506" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC506" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD506" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE506" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF506" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG506" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH506" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI506" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ506" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK506" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL506">
         <v>1</v>
       </c>
@@ -82839,39 +82476,6 @@
       <c r="AY507">
         <v>24</v>
       </c>
-      <c r="BA507">
-        <v>33</v>
-      </c>
-      <c r="BB507" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC507" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD507" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE507" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF507" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG507" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH507" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI507" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ507" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK507" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL507">
         <v>1</v>
       </c>
@@ -83000,39 +82604,6 @@
       <c r="AY508">
         <v>23</v>
       </c>
-      <c r="BA508">
-        <v>33</v>
-      </c>
-      <c r="BB508" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC508" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD508" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE508" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF508" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG508" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH508" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI508" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ508" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK508" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL508">
         <v>1</v>
       </c>
@@ -83161,39 +82732,6 @@
       <c r="AY509">
         <v>24</v>
       </c>
-      <c r="BA509">
-        <v>34</v>
-      </c>
-      <c r="BB509" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC509" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD509" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE509" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF509" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG509" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH509" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI509" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ509" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK509" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL509">
         <v>0</v>
       </c>
@@ -83319,39 +82857,6 @@
       <c r="AY510">
         <v>24</v>
       </c>
-      <c r="BA510">
-        <v>34</v>
-      </c>
-      <c r="BB510" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC510" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD510" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE510" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF510" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG510" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH510" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI510" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BJ510" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK510" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL510">
         <v>1</v>
       </c>
@@ -83480,39 +82985,6 @@
       <c r="AY511">
         <v>23</v>
       </c>
-      <c r="BA511">
-        <v>23</v>
-      </c>
-      <c r="BB511" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC511" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD511" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE511" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF511" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG511" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH511" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI511" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ511" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK511" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL511">
         <v>1</v>
       </c>
@@ -83641,39 +83113,6 @@
       <c r="AY512">
         <v>24</v>
       </c>
-      <c r="BA512">
-        <v>34</v>
-      </c>
-      <c r="BB512" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC512" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD512" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE512" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF512" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG512" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH512" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI512" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BJ512" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK512" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL512">
         <v>1</v>
       </c>
@@ -83802,39 +83241,6 @@
       <c r="AY513">
         <v>24</v>
       </c>
-      <c r="BA513">
-        <v>33</v>
-      </c>
-      <c r="BB513" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC513" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD513" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE513" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF513" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG513" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH513" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI513" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ513" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK513" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL513">
         <v>1</v>
       </c>
@@ -83963,39 +83369,6 @@
       <c r="AY514">
         <v>24</v>
       </c>
-      <c r="BA514">
-        <v>33</v>
-      </c>
-      <c r="BB514" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC514" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD514" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE514" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF514" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG514" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH514" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BI514" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ514" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK514" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL514">
         <v>1</v>
       </c>
@@ -84121,39 +83494,6 @@
       <c r="AY515">
         <v>23</v>
       </c>
-      <c r="BA515">
-        <v>33</v>
-      </c>
-      <c r="BB515" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC515" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD515" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BE515" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF515" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG515" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH515" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI515" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ515" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK515" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL515">
         <v>1</v>
       </c>
@@ -84282,39 +83622,6 @@
       <c r="AY516">
         <v>24</v>
       </c>
-      <c r="BA516">
-        <v>33</v>
-      </c>
-      <c r="BB516" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC516" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD516" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE516" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF516" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG516" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH516" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI516" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BJ516" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK516" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL516">
         <v>1</v>
       </c>
@@ -84440,39 +83747,6 @@
       <c r="AY517">
         <v>24</v>
       </c>
-      <c r="BA517">
-        <v>34</v>
-      </c>
-      <c r="BB517" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC517" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD517" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE517" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF517" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG517" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH517" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI517" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ517" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK517" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL517">
         <v>1</v>
       </c>
@@ -84851,12 +84125,6 @@
       <c r="AY520">
         <v>24</v>
       </c>
-      <c r="BA520">
-        <v>33</v>
-      </c>
-      <c r="BD520" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL520">
         <v>1</v>
       </c>
@@ -84985,12 +84253,6 @@
       <c r="AY521">
         <v>24</v>
       </c>
-      <c r="BA521">
-        <v>34</v>
-      </c>
-      <c r="BD521" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL521">
         <v>1</v>
       </c>
@@ -85032,9 +84294,6 @@
       <c r="L522">
         <v>5</v>
       </c>
-      <c r="BD522" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL522">
         <v>1</v>
       </c>
@@ -85160,12 +84419,6 @@
       <c r="AY523">
         <v>24</v>
       </c>
-      <c r="BA523">
-        <v>23</v>
-      </c>
-      <c r="BD523" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL523">
         <v>1</v>
       </c>
@@ -85291,39 +84544,6 @@
       <c r="AY524">
         <v>24</v>
       </c>
-      <c r="BA524">
-        <v>33</v>
-      </c>
-      <c r="BB524" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC524" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD524" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE524" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF524" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG524" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH524" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI524" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ524" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK524" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL524">
         <v>1</v>
       </c>
@@ -85452,39 +84672,6 @@
       <c r="AY525">
         <v>24</v>
       </c>
-      <c r="BA525">
-        <v>23</v>
-      </c>
-      <c r="BB525" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC525" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD525" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE525" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF525" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG525" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH525" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI525" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ525" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK525" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL525">
         <v>0</v>
       </c>
@@ -85613,39 +84800,6 @@
       <c r="AY526">
         <v>20</v>
       </c>
-      <c r="BA526">
-        <v>34</v>
-      </c>
-      <c r="BB526" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC526" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD526" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE526" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF526" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG526" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH526" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI526" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ526" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK526" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL526">
         <v>1</v>
       </c>
@@ -85771,39 +84925,6 @@
       <c r="AY527">
         <v>22</v>
       </c>
-      <c r="BA527">
-        <v>33</v>
-      </c>
-      <c r="BB527" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC527" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD527" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE527" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF527" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG527" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH527" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI527" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ527" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK527" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL527">
         <v>1</v>
       </c>
@@ -85923,39 +85044,6 @@
       <c r="AY528">
         <v>23</v>
       </c>
-      <c r="BA528">
-        <v>34</v>
-      </c>
-      <c r="BB528" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC528" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD528" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE528" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF528" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG528" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH528" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI528" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ528" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK528" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL528">
         <v>1</v>
       </c>
@@ -86081,39 +85169,6 @@
       <c r="AY529">
         <v>24</v>
       </c>
-      <c r="BA529">
-        <v>33</v>
-      </c>
-      <c r="BB529" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC529" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD529" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE529" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF529" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG529" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH529" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI529" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ529" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK529" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL529">
         <v>1</v>
       </c>
@@ -86361,39 +85416,6 @@
       <c r="AY531">
         <v>23</v>
       </c>
-      <c r="BA531">
-        <v>33</v>
-      </c>
-      <c r="BB531" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC531" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD531" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE531" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF531" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG531" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH531" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI531" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ531" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK531" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL531">
         <v>1</v>
       </c>
@@ -86650,39 +85672,6 @@
       <c r="AY533">
         <v>24</v>
       </c>
-      <c r="BA533">
-        <v>34</v>
-      </c>
-      <c r="BB533" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC533" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD533" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE533" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF533" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG533" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH533" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI533" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ533" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK533" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL533">
         <v>1</v>
       </c>
@@ -86808,39 +85797,6 @@
       <c r="AY534">
         <v>23</v>
       </c>
-      <c r="BA534">
-        <v>33</v>
-      </c>
-      <c r="BB534" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC534" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD534" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE534" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF534" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG534" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH534" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI534" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ534" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK534" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL534">
         <v>1</v>
       </c>
@@ -86960,39 +85916,6 @@
       <c r="AY535">
         <v>20</v>
       </c>
-      <c r="BA535">
-        <v>33</v>
-      </c>
-      <c r="BB535" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC535" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD535" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE535" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF535" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG535" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH535" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI535" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ535" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK535" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL535">
         <v>0</v>
       </c>
@@ -87034,12 +85957,6 @@
       <c r="L536">
         <v>5</v>
       </c>
-      <c r="BA536">
-        <v>34</v>
-      </c>
-      <c r="BD536" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL536">
         <v>1</v>
       </c>
@@ -87165,12 +86082,6 @@
       <c r="AY537">
         <v>23</v>
       </c>
-      <c r="BA537">
-        <v>34</v>
-      </c>
-      <c r="BD537" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL537">
         <v>1</v>
       </c>
@@ -87299,39 +86210,6 @@
       <c r="AY538">
         <v>23</v>
       </c>
-      <c r="BA538">
-        <v>33</v>
-      </c>
-      <c r="BB538" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC538" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD538" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE538" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF538" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG538" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH538" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI538" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BJ538" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK538" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL538">
         <v>1</v>
       </c>
@@ -87454,39 +86332,6 @@
       <c r="AY539">
         <v>19</v>
       </c>
-      <c r="BA539">
-        <v>33</v>
-      </c>
-      <c r="BB539" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC539" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD539" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE539" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF539" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG539" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH539" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI539" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ539" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK539" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL539">
         <v>1</v>
       </c>
@@ -87612,39 +86457,6 @@
       <c r="AY540">
         <v>24</v>
       </c>
-      <c r="BA540">
-        <v>33</v>
-      </c>
-      <c r="BB540" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC540" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD540" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE540" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF540" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG540" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH540" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI540" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ540" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK540" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL540">
         <v>1</v>
       </c>
@@ -87773,39 +86585,6 @@
       <c r="AY541">
         <v>24</v>
       </c>
-      <c r="BA541">
-        <v>33</v>
-      </c>
-      <c r="BB541" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC541" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD541" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE541" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF541" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG541" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH541" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI541" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ541" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK541" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL541">
         <v>1</v>
       </c>
@@ -87934,39 +86713,6 @@
       <c r="AY542">
         <v>20</v>
       </c>
-      <c r="BA542">
-        <v>33</v>
-      </c>
-      <c r="BB542" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC542" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD542" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BE542" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF542" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG542" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH542" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI542" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ542" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK542" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL542">
         <v>1</v>
       </c>
@@ -88029,39 +86775,6 @@
       <c r="AK543">
         <v>24</v>
       </c>
-      <c r="BA543">
-        <v>33</v>
-      </c>
-      <c r="BB543" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC543" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD543" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE543" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF543" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG543" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH543" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI543" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ543" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK543" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL543">
         <v>1</v>
       </c>
@@ -88124,39 +86837,6 @@
       <c r="AK544">
         <v>31</v>
       </c>
-      <c r="BA544">
-        <v>34</v>
-      </c>
-      <c r="BB544" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC544" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD544" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE544" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF544" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG544" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH544" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI544" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ544" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK544" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL544">
         <v>1</v>
       </c>
@@ -88219,39 +86899,6 @@
       <c r="AK545">
         <v>29</v>
       </c>
-      <c r="BA545">
-        <v>33</v>
-      </c>
-      <c r="BB545" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC545" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD545" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE545" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF545" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG545" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH545" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BI545" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ545" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK545" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL545">
         <v>1</v>
       </c>
@@ -88380,12 +87027,6 @@
       <c r="AY546">
         <v>21</v>
       </c>
-      <c r="BA546">
-        <v>24</v>
-      </c>
-      <c r="BD546" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL546">
         <v>1</v>
       </c>
@@ -88514,39 +87155,6 @@
       <c r="AY547">
         <v>24</v>
       </c>
-      <c r="BA547">
-        <v>23</v>
-      </c>
-      <c r="BB547" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC547" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD547" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE547" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF547" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG547" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH547" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BI547" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ547" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK547" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL547">
         <v>1</v>
       </c>
@@ -88675,39 +87283,6 @@
       <c r="AY548">
         <v>24</v>
       </c>
-      <c r="BA548">
-        <v>34</v>
-      </c>
-      <c r="BB548" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC548" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD548" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE548" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF548" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG548" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH548" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI548" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ548" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK548" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL548">
         <v>1</v>
       </c>
@@ -88836,39 +87411,6 @@
       <c r="AY549">
         <v>23</v>
       </c>
-      <c r="BA549">
-        <v>33</v>
-      </c>
-      <c r="BB549" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC549" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD549" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE549" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF549" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG549" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH549" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI549" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ549" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK549" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL549">
         <v>1</v>
       </c>
@@ -88997,39 +87539,6 @@
       <c r="AY550">
         <v>24</v>
       </c>
-      <c r="BA550">
-        <v>33</v>
-      </c>
-      <c r="BB550" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC550" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD550" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE550" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF550" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG550" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH550" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI550" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ550" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK550" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL550">
         <v>1</v>
       </c>
@@ -89092,39 +87601,6 @@
       <c r="AK551">
         <v>35</v>
       </c>
-      <c r="BA551">
-        <v>33</v>
-      </c>
-      <c r="BB551" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC551" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD551" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE551" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF551" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG551" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH551" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI551" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ551" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK551" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL551">
         <v>1</v>
       </c>
@@ -89181,12 +87657,6 @@
       <c r="AK552">
         <v>36</v>
       </c>
-      <c r="BA552">
-        <v>34</v>
-      </c>
-      <c r="BD552" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL552">
         <v>1</v>
       </c>
@@ -89249,39 +87719,6 @@
       <c r="AK553">
         <v>33</v>
       </c>
-      <c r="BA553">
-        <v>34</v>
-      </c>
-      <c r="BB553" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC553" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD553" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE553" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF553" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG553" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH553" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI553" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ553" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK553" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL553">
         <v>1</v>
       </c>
@@ -89410,39 +87847,6 @@
       <c r="AY554">
         <v>24</v>
       </c>
-      <c r="BA554">
-        <v>23</v>
-      </c>
-      <c r="BB554" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC554" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD554" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE554" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF554" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG554" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH554" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BI554" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ554" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK554" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL554">
         <v>1</v>
       </c>
@@ -89568,12 +87972,6 @@
       <c r="AY555">
         <v>23</v>
       </c>
-      <c r="BA555">
-        <v>33</v>
-      </c>
-      <c r="BD555" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL555">
         <v>1</v>
       </c>
@@ -89636,39 +88034,6 @@
       <c r="AK556">
         <v>22</v>
       </c>
-      <c r="BA556">
-        <v>34</v>
-      </c>
-      <c r="BB556" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC556" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD556" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE556" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF556" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG556" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH556" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI556" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ556" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK556" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL556">
         <v>1</v>
       </c>
@@ -89731,39 +88096,6 @@
       <c r="AK557">
         <v>24</v>
       </c>
-      <c r="BA557">
-        <v>33</v>
-      </c>
-      <c r="BB557" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC557" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD557" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE557" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF557" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG557" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH557" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI557" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ557" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK557" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL557">
         <v>0</v>
       </c>
@@ -89805,39 +88137,6 @@
       <c r="L558">
         <v>5</v>
       </c>
-      <c r="BA558">
-        <v>23</v>
-      </c>
-      <c r="BB558" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC558" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD558" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE558" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF558" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG558" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH558" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BI558" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ558" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK558" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL558">
         <v>1</v>
       </c>
@@ -89879,39 +88178,6 @@
       <c r="L559">
         <v>5</v>
       </c>
-      <c r="BA559">
-        <v>34</v>
-      </c>
-      <c r="BB559" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC559" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD559" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE559" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF559" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG559" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH559" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI559" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ559" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK559" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL559">
         <v>1</v>
       </c>
@@ -90037,39 +88303,6 @@
       <c r="AY560">
         <v>24</v>
       </c>
-      <c r="BA560">
-        <v>33</v>
-      </c>
-      <c r="BB560" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC560" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD560" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BE560" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF560" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG560" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH560" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI560" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ560" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK560" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL560">
         <v>1</v>
       </c>
@@ -90189,39 +88422,6 @@
       <c r="AW561">
         <v>24</v>
       </c>
-      <c r="BA561">
-        <v>34</v>
-      </c>
-      <c r="BB561" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC561" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD561" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE561" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF561" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG561" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH561" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI561" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ561" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK561" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL561">
         <v>1</v>
       </c>
@@ -90344,39 +88544,6 @@
       <c r="AY562">
         <v>21</v>
       </c>
-      <c r="BA562">
-        <v>33</v>
-      </c>
-      <c r="BB562" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC562" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD562" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BE562" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF562" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG562" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH562" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI562" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ562" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK562" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL562">
         <v>1</v>
       </c>
@@ -90502,39 +88669,6 @@
       <c r="AY563">
         <v>17</v>
       </c>
-      <c r="BA563">
-        <v>23</v>
-      </c>
-      <c r="BB563" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC563" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD563" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE563" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF563" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG563" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH563" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI563" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ563" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK563" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL563">
         <v>0</v>
       </c>
@@ -90663,39 +88797,6 @@
       <c r="AY564">
         <v>23</v>
       </c>
-      <c r="BA564">
-        <v>33</v>
-      </c>
-      <c r="BB564" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC564" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD564" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE564" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF564" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG564" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH564" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI564" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BJ564" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK564" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL564">
         <v>1</v>
       </c>
@@ -90737,39 +88838,6 @@
       <c r="L565">
         <v>5</v>
       </c>
-      <c r="BA565">
-        <v>33</v>
-      </c>
-      <c r="BB565" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC565" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD565" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE565" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF565" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG565" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH565" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI565" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ565" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK565" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL565">
         <v>1</v>
       </c>
@@ -90886,39 +88954,6 @@
       <c r="AY566">
         <v>24</v>
       </c>
-      <c r="BA566">
-        <v>33</v>
-      </c>
-      <c r="BB566" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC566" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD566" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE566" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF566" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG566" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH566" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI566" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ566" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK566" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL566">
         <v>1</v>
       </c>
@@ -91047,12 +89082,6 @@
       <c r="AY567">
         <v>24</v>
       </c>
-      <c r="BA567">
-        <v>34</v>
-      </c>
-      <c r="BD567" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL567">
         <v>1</v>
       </c>
@@ -91181,39 +89210,6 @@
       <c r="AY568">
         <v>23</v>
       </c>
-      <c r="BA568">
-        <v>34</v>
-      </c>
-      <c r="BB568" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC568" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD568" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE568" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF568" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG568" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH568" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI568" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ568" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK568" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL568">
         <v>1</v>
       </c>
@@ -91342,39 +89338,6 @@
       <c r="AY569">
         <v>22</v>
       </c>
-      <c r="BA569">
-        <v>22</v>
-      </c>
-      <c r="BB569" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC569" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD569" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE569" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF569" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG569" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH569" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI569" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ569" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK569" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL569">
         <v>1</v>
       </c>
@@ -91503,39 +89466,6 @@
       <c r="AY570">
         <v>24</v>
       </c>
-      <c r="BA570">
-        <v>33</v>
-      </c>
-      <c r="BB570" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC570" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD570" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE570" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF570" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG570" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH570" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI570" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ570" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK570" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL570">
         <v>1</v>
       </c>
@@ -91664,39 +89594,6 @@
       <c r="AY571">
         <v>22</v>
       </c>
-      <c r="BA571">
-        <v>34</v>
-      </c>
-      <c r="BB571" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC571" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD571" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE571" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF571" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG571" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH571" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI571" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ571" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK571" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL571">
         <v>1</v>
       </c>
@@ -91825,12 +89722,6 @@
       <c r="AY572">
         <v>22</v>
       </c>
-      <c r="BA572">
-        <v>34</v>
-      </c>
-      <c r="BD572" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL572">
         <v>1</v>
       </c>
@@ -91893,12 +89784,6 @@
       <c r="AK573">
         <v>32</v>
       </c>
-      <c r="BA573">
-        <v>33</v>
-      </c>
-      <c r="BD573" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL573">
         <v>1</v>
       </c>
@@ -91940,12 +89825,6 @@
       <c r="L574">
         <v>5</v>
       </c>
-      <c r="BA574">
-        <v>33</v>
-      </c>
-      <c r="BD574" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL574">
         <v>1</v>
       </c>
@@ -92074,39 +89953,6 @@
       <c r="AY575">
         <v>24</v>
       </c>
-      <c r="BA575">
-        <v>33</v>
-      </c>
-      <c r="BB575" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC575" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD575" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE575" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF575" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG575" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH575" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI575" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BJ575" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK575" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL575">
         <v>1</v>
       </c>
@@ -92235,39 +90081,6 @@
       <c r="AY576">
         <v>22</v>
       </c>
-      <c r="BA576">
-        <v>33</v>
-      </c>
-      <c r="BB576" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC576" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD576" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE576" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF576" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG576" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH576" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI576" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BJ576" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK576" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL576">
         <v>1</v>
       </c>
@@ -92396,39 +90209,6 @@
       <c r="AY577">
         <v>16</v>
       </c>
-      <c r="BA577">
-        <v>33</v>
-      </c>
-      <c r="BB577" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC577" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD577" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE577" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF577" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG577" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH577" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI577" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ577" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK577" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL577">
         <v>1</v>
       </c>
@@ -92557,39 +90337,6 @@
       <c r="AY578">
         <v>24</v>
       </c>
-      <c r="BA578">
-        <v>34</v>
-      </c>
-      <c r="BB578" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC578" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD578" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE578" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF578" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG578" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH578" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI578" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ578" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK578" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL578">
         <v>1</v>
       </c>
@@ -92718,39 +90465,6 @@
       <c r="AY579">
         <v>23</v>
       </c>
-      <c r="BA579">
-        <v>33</v>
-      </c>
-      <c r="BB579" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC579" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD579" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE579" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF579" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG579" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH579" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI579" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BJ579" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK579" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL579">
         <v>1</v>
       </c>
@@ -92879,12 +90593,6 @@
       <c r="AY580">
         <v>23</v>
       </c>
-      <c r="BA580">
-        <v>33</v>
-      </c>
-      <c r="BD580" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL580">
         <v>1</v>
       </c>
@@ -93013,39 +90721,6 @@
       <c r="AY581">
         <v>21</v>
       </c>
-      <c r="BA581">
-        <v>23</v>
-      </c>
-      <c r="BB581" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC581" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD581" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE581" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF581" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG581" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH581" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI581" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ581" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK581" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL581">
         <v>1</v>
       </c>
@@ -93174,12 +90849,6 @@
       <c r="AY582">
         <v>22</v>
       </c>
-      <c r="BA582">
-        <v>33</v>
-      </c>
-      <c r="BD582" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL582">
         <v>1</v>
       </c>
@@ -93308,39 +90977,6 @@
       <c r="AY583">
         <v>24</v>
       </c>
-      <c r="BA583">
-        <v>33</v>
-      </c>
-      <c r="BB583" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC583" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD583" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE583" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF583" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG583" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH583" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI583" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ583" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK583" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL583">
         <v>1</v>
       </c>
@@ -93469,39 +91105,6 @@
       <c r="AY584">
         <v>24</v>
       </c>
-      <c r="BA584">
-        <v>33</v>
-      </c>
-      <c r="BB584" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC584" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD584" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE584" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF584" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG584" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH584" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI584" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ584" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK584" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL584">
         <v>1</v>
       </c>
@@ -93630,39 +91233,6 @@
       <c r="AY585">
         <v>23</v>
       </c>
-      <c r="BA585">
-        <v>33</v>
-      </c>
-      <c r="BB585" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC585" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD585" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE585" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF585" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG585" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH585" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI585" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ585" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK585" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL585">
         <v>1</v>
       </c>
@@ -93791,39 +91361,6 @@
       <c r="AY586">
         <v>24</v>
       </c>
-      <c r="BA586">
-        <v>33</v>
-      </c>
-      <c r="BB586" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC586" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD586" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE586" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF586" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG586" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH586" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI586" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ586" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK586" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL586">
         <v>1</v>
       </c>
@@ -93952,39 +91489,6 @@
       <c r="AY587">
         <v>23</v>
       </c>
-      <c r="BA587">
-        <v>33</v>
-      </c>
-      <c r="BB587" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC587" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD587" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE587" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF587" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG587" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH587" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI587" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ587" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK587" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL587">
         <v>1</v>
       </c>
@@ -94113,39 +91617,6 @@
       <c r="AY588">
         <v>24</v>
       </c>
-      <c r="BA588">
-        <v>33</v>
-      </c>
-      <c r="BB588" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC588" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD588" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE588" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF588" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG588" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH588" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI588" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ588" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK588" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL588">
         <v>1</v>
       </c>
@@ -94274,39 +91745,6 @@
       <c r="AY589">
         <v>23</v>
       </c>
-      <c r="BA589">
-        <v>34</v>
-      </c>
-      <c r="BB589" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC589" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD589" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE589" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF589" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG589" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH589" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI589" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ589" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK589" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL589">
         <v>1</v>
       </c>
@@ -94435,39 +91873,6 @@
       <c r="AY590">
         <v>24</v>
       </c>
-      <c r="BA590">
-        <v>34</v>
-      </c>
-      <c r="BB590" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC590" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD590" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE590" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF590" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG590" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH590" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI590" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ590" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK590" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL590">
         <v>1</v>
       </c>
@@ -94596,39 +92001,6 @@
       <c r="AY591">
         <v>22</v>
       </c>
-      <c r="BA591">
-        <v>33</v>
-      </c>
-      <c r="BB591" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC591" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD591" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE591" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF591" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG591" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH591" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI591" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ591" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK591" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL591">
         <v>1</v>
       </c>
@@ -94754,39 +92126,6 @@
       <c r="AY592">
         <v>21</v>
       </c>
-      <c r="BA592">
-        <v>23</v>
-      </c>
-      <c r="BB592" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC592" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD592" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE592" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF592" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG592" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH592" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI592" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BJ592" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK592" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL592">
         <v>1</v>
       </c>
@@ -94915,39 +92254,6 @@
       <c r="AY593">
         <v>24</v>
       </c>
-      <c r="BA593">
-        <v>33</v>
-      </c>
-      <c r="BB593" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC593" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD593" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE593" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF593" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG593" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH593" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI593" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ593" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK593" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL593">
         <v>1</v>
       </c>
@@ -95076,39 +92382,6 @@
       <c r="AY594">
         <v>23</v>
       </c>
-      <c r="BA594">
-        <v>23</v>
-      </c>
-      <c r="BB594" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC594" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD594" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE594" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF594" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG594" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH594" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI594" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ594" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK594" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL594">
         <v>1</v>
       </c>
@@ -95228,39 +92501,6 @@
       <c r="AY595">
         <v>23</v>
       </c>
-      <c r="BA595">
-        <v>33</v>
-      </c>
-      <c r="BB595" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC595" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD595" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE595" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF595" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG595" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH595" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BI595" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ595" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK595" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL595">
         <v>1</v>
       </c>
@@ -95389,39 +92629,6 @@
       <c r="AY596">
         <v>24</v>
       </c>
-      <c r="BA596">
-        <v>33</v>
-      </c>
-      <c r="BB596" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC596" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD596" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE596" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF596" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG596" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH596" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI596" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ596" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK596" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL596">
         <v>1</v>
       </c>
@@ -95550,39 +92757,6 @@
       <c r="AY597">
         <v>24</v>
       </c>
-      <c r="BA597">
-        <v>33</v>
-      </c>
-      <c r="BB597" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC597" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD597" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BE597" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF597" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG597" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH597" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI597" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ597" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK597" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL597">
         <v>1</v>
       </c>
@@ -95711,39 +92885,6 @@
       <c r="AY598">
         <v>23</v>
       </c>
-      <c r="BA598">
-        <v>33</v>
-      </c>
-      <c r="BB598" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC598" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD598" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE598" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF598" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG598" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH598" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI598" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ598" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK598" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL598">
         <v>1</v>
       </c>
@@ -95872,39 +93013,6 @@
       <c r="AY599">
         <v>23</v>
       </c>
-      <c r="BA599">
-        <v>33</v>
-      </c>
-      <c r="BB599" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC599" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD599" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BE599" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF599" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG599" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH599" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI599" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ599" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK599" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL599">
         <v>1</v>
       </c>
@@ -96033,39 +93141,6 @@
       <c r="AY600">
         <v>24</v>
       </c>
-      <c r="BA600">
-        <v>33</v>
-      </c>
-      <c r="BB600" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC600" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD600" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE600" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF600" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG600" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH600" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI600" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ600" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK600" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL600">
         <v>1</v>
       </c>
@@ -96319,39 +93394,6 @@
       <c r="AY602">
         <v>24</v>
       </c>
-      <c r="BA602">
-        <v>33</v>
-      </c>
-      <c r="BB602" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC602" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD602" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE602" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF602" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG602" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH602" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI602" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ602" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK602" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL602">
         <v>1</v>
       </c>
@@ -96477,39 +93519,6 @@
       <c r="AY603">
         <v>22</v>
       </c>
-      <c r="BA603">
-        <v>34</v>
-      </c>
-      <c r="BB603" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC603" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD603" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BE603" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BF603" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG603" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH603" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI603" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ603" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK603" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL603">
         <v>1</v>
       </c>
@@ -96638,39 +93647,6 @@
       <c r="AY604">
         <v>20</v>
       </c>
-      <c r="BA604">
-        <v>33</v>
-      </c>
-      <c r="BB604" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC604" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD604" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE604" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF604" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG604" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH604" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI604" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ604" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK604" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL604">
         <v>1</v>
       </c>
@@ -96799,39 +93775,6 @@
       <c r="AY605">
         <v>22</v>
       </c>
-      <c r="BA605">
-        <v>33</v>
-      </c>
-      <c r="BB605" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC605" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD605" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE605" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF605" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG605" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH605" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI605" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ605" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK605" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL605">
         <v>1</v>
       </c>
@@ -97085,39 +94028,6 @@
       <c r="AY607">
         <v>24</v>
       </c>
-      <c r="BA607">
-        <v>34</v>
-      </c>
-      <c r="BB607" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC607" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD607" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE607" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF607" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG607" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH607" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI607" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ607" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK607" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL607">
         <v>1</v>
       </c>
@@ -97243,39 +94153,6 @@
       <c r="AY608">
         <v>24</v>
       </c>
-      <c r="BA608">
-        <v>44</v>
-      </c>
-      <c r="BB608" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC608" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD608" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE608" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF608" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG608" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH608" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI608" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ608" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK608" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL608">
         <v>1</v>
       </c>
@@ -97401,39 +94278,6 @@
       <c r="AY609">
         <v>22</v>
       </c>
-      <c r="BA609">
-        <v>33</v>
-      </c>
-      <c r="BB609" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC609" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD609" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE609" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF609" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG609" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH609" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI609" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BJ609" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK609" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL609">
         <v>1</v>
       </c>
@@ -97684,39 +94528,6 @@
       <c r="AY611">
         <v>24</v>
       </c>
-      <c r="BA611">
-        <v>33</v>
-      </c>
-      <c r="BB611" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC611" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD611" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE611" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF611" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG611" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH611" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI611" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ611" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK611" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL611">
         <v>1</v>
       </c>
@@ -98095,39 +94906,6 @@
       <c r="AY614">
         <v>24</v>
       </c>
-      <c r="BA614">
-        <v>33</v>
-      </c>
-      <c r="BB614" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC614" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD614" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE614" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF614" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG614" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH614" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI614" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ614" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK614" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL614">
         <v>1</v>
       </c>
@@ -98256,39 +95034,6 @@
       <c r="AY615">
         <v>23</v>
       </c>
-      <c r="BA615">
-        <v>33</v>
-      </c>
-      <c r="BB615" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC615" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD615" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE615" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF615" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG615" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH615" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BI615" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ615" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK615" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL615">
         <v>1</v>
       </c>
@@ -98414,39 +95159,6 @@
       <c r="AY616">
         <v>10</v>
       </c>
-      <c r="BA616">
-        <v>33</v>
-      </c>
-      <c r="BB616" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC616" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD616" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE616" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF616" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG616" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH616" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI616" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BJ616" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK616" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL616">
         <v>1</v>
       </c>
@@ -98572,39 +95284,6 @@
       <c r="AY617">
         <v>19</v>
       </c>
-      <c r="BA617">
-        <v>33</v>
-      </c>
-      <c r="BB617" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC617" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD617" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE617" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF617" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG617" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH617" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI617" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ617" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK617" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL617">
         <v>1</v>
       </c>
@@ -98730,12 +95409,6 @@
       <c r="AY618">
         <v>24</v>
       </c>
-      <c r="BA618">
-        <v>33</v>
-      </c>
-      <c r="BD618" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL618">
         <v>1</v>
       </c>
@@ -98864,12 +95537,6 @@
       <c r="AY619">
         <v>23</v>
       </c>
-      <c r="BA619">
-        <v>33</v>
-      </c>
-      <c r="BD619" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL619">
         <v>1</v>
       </c>
@@ -98992,39 +95659,6 @@
       <c r="AY620">
         <v>24</v>
       </c>
-      <c r="BA620">
-        <v>33</v>
-      </c>
-      <c r="BB620" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC620" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD620" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE620" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF620" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG620" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH620" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI620" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ620" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK620" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL620">
         <v>1</v>
       </c>
@@ -99150,39 +95784,6 @@
       <c r="AY621">
         <v>24</v>
       </c>
-      <c r="BA621">
-        <v>33</v>
-      </c>
-      <c r="BB621" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC621" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD621" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE621" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF621" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG621" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH621" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI621" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ621" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK621" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL621">
         <v>1</v>
       </c>
@@ -99308,12 +95909,6 @@
       <c r="AY622">
         <v>24</v>
       </c>
-      <c r="BA622">
-        <v>33</v>
-      </c>
-      <c r="BD622" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL622">
         <v>1</v>
       </c>
@@ -99439,12 +96034,6 @@
       <c r="AY623">
         <v>24</v>
       </c>
-      <c r="BA623">
-        <v>33</v>
-      </c>
-      <c r="BD623" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL623">
         <v>1</v>
       </c>
@@ -99570,12 +96159,6 @@
       <c r="AY624">
         <v>24</v>
       </c>
-      <c r="BA624">
-        <v>33</v>
-      </c>
-      <c r="BD624" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL624">
         <v>1</v>
       </c>
@@ -99829,39 +96412,6 @@
       <c r="AY626">
         <v>23</v>
       </c>
-      <c r="BA626">
-        <v>33</v>
-      </c>
-      <c r="BB626" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC626" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD626" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE626" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF626" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG626" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH626" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI626" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ626" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK626" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL626">
         <v>1</v>
       </c>
@@ -99987,39 +96537,6 @@
       <c r="AY627">
         <v>24</v>
       </c>
-      <c r="BA627">
-        <v>34</v>
-      </c>
-      <c r="BB627" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC627" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD627" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE627" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF627" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG627" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH627" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI627" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ627" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK627" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL627">
         <v>1</v>
       </c>
@@ -100145,39 +96662,6 @@
       <c r="AY628">
         <v>21</v>
       </c>
-      <c r="BA628">
-        <v>34</v>
-      </c>
-      <c r="BB628" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC628" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD628" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE628" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF628" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG628" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH628" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI628" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ628" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK628" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL628">
         <v>1</v>
       </c>
@@ -100303,39 +96787,6 @@
       <c r="AY629">
         <v>24</v>
       </c>
-      <c r="BA629">
-        <v>33</v>
-      </c>
-      <c r="BB629" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC629" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD629" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE629" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF629" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG629" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH629" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI629" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ629" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK629" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL629">
         <v>1</v>
       </c>
@@ -100398,39 +96849,6 @@
       <c r="AK630">
         <v>33</v>
       </c>
-      <c r="BA630">
-        <v>34</v>
-      </c>
-      <c r="BB630" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC630" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD630" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE630" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF630" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG630" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH630" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI630" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ630" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK630" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL630">
         <v>1</v>
       </c>
@@ -100493,39 +96911,6 @@
       <c r="AK631">
         <v>31</v>
       </c>
-      <c r="BA631">
-        <v>33</v>
-      </c>
-      <c r="BB631" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC631" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD631" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE631" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF631" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG631" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH631" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI631" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ631" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK631" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL631">
         <v>1</v>
       </c>
@@ -100651,39 +97036,6 @@
       <c r="AY632">
         <v>24</v>
       </c>
-      <c r="BA632">
-        <v>33</v>
-      </c>
-      <c r="BB632" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC632" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD632" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE632" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF632" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG632" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH632" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI632" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ632" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK632" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL632">
         <v>1</v>
       </c>
@@ -100746,39 +97098,6 @@
       <c r="AK633">
         <v>35</v>
       </c>
-      <c r="BA633">
-        <v>34</v>
-      </c>
-      <c r="BB633" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC633" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD633" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE633" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF633" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG633" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH633" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI633" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ633" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK633" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL633">
         <v>1</v>
       </c>
@@ -100841,39 +97160,6 @@
       <c r="AK634">
         <v>35</v>
       </c>
-      <c r="BA634">
-        <v>34</v>
-      </c>
-      <c r="BB634" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC634" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD634" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE634" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF634" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG634" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH634" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI634" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ634" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK634" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL634">
         <v>1</v>
       </c>
@@ -101002,39 +97288,6 @@
       <c r="AY635">
         <v>23</v>
       </c>
-      <c r="BA635">
-        <v>33</v>
-      </c>
-      <c r="BB635" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC635" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD635" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE635" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF635" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG635" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH635" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI635" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ635" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK635" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL635">
         <v>1</v>
       </c>
@@ -101160,39 +97413,6 @@
       <c r="AY636">
         <v>23</v>
       </c>
-      <c r="BA636">
-        <v>34</v>
-      </c>
-      <c r="BB636" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC636" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD636" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE636" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF636" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG636" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH636" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI636" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ636" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK636" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL636">
         <v>1</v>
       </c>
@@ -101318,39 +97538,6 @@
       <c r="AY637">
         <v>24</v>
       </c>
-      <c r="BA637">
-        <v>34</v>
-      </c>
-      <c r="BB637" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC637" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD637" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE637" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF637" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG637" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH637" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI637" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ637" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK637" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL637">
         <v>1</v>
       </c>
@@ -101476,39 +97663,6 @@
       <c r="AY638">
         <v>23</v>
       </c>
-      <c r="BA638">
-        <v>33</v>
-      </c>
-      <c r="BB638" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC638" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD638" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE638" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF638" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG638" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH638" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI638" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ638" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK638" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL638">
         <v>1</v>
       </c>
@@ -101634,39 +97788,6 @@
       <c r="AY639">
         <v>24</v>
       </c>
-      <c r="BA639">
-        <v>34</v>
-      </c>
-      <c r="BB639" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC639" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD639" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE639" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF639" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG639" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH639" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI639" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ639" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK639" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL639">
         <v>1</v>
       </c>
@@ -101795,39 +97916,6 @@
       <c r="AY640">
         <v>23</v>
       </c>
-      <c r="BA640">
-        <v>34</v>
-      </c>
-      <c r="BB640" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC640" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD640" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE640" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF640" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG640" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH640" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI640" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ640" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK640" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL640">
         <v>1</v>
       </c>
@@ -101956,39 +98044,6 @@
       <c r="AY641">
         <v>24</v>
       </c>
-      <c r="BA641">
-        <v>33</v>
-      </c>
-      <c r="BB641" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC641" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD641" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE641" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF641" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG641" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH641" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI641" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ641" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK641" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL641">
         <v>1</v>
       </c>
@@ -102114,39 +98169,6 @@
       <c r="AY642">
         <v>24</v>
       </c>
-      <c r="BA642">
-        <v>34</v>
-      </c>
-      <c r="BB642" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC642" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD642" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE642" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF642" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG642" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH642" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI642" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ642" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK642" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL642">
         <v>1</v>
       </c>
@@ -102275,39 +98297,6 @@
       <c r="AY643">
         <v>24</v>
       </c>
-      <c r="BA643">
-        <v>44</v>
-      </c>
-      <c r="BB643" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC643" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD643" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE643" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF643" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG643" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH643" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI643" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ643" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK643" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL643">
         <v>1</v>
       </c>
@@ -102430,39 +98419,6 @@
       <c r="AY644">
         <v>24</v>
       </c>
-      <c r="BA644">
-        <v>33</v>
-      </c>
-      <c r="BB644" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC644" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD644" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BE644" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF644" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG644" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH644" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI644" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ644" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK644" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL644">
         <v>1</v>
       </c>
@@ -102591,39 +98547,6 @@
       <c r="AY645">
         <v>22</v>
       </c>
-      <c r="BA645">
-        <v>34</v>
-      </c>
-      <c r="BB645" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC645" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD645" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE645" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF645" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG645" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH645" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI645" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ645" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK645" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL645">
         <v>1</v>
       </c>
@@ -102752,39 +98675,6 @@
       <c r="AY646">
         <v>24</v>
       </c>
-      <c r="BA646">
-        <v>33</v>
-      </c>
-      <c r="BB646" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC646" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD646" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE646" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF646" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG646" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH646" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI646" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ646" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK646" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL646">
         <v>1</v>
       </c>
@@ -102904,39 +98794,6 @@
       <c r="AY647">
         <v>24</v>
       </c>
-      <c r="BA647">
-        <v>34</v>
-      </c>
-      <c r="BB647" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC647" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD647" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE647" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF647" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG647" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH647" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI647" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ647" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK647" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL647">
         <v>1</v>
       </c>
@@ -103062,39 +98919,6 @@
       <c r="AY648">
         <v>24</v>
       </c>
-      <c r="BA648">
-        <v>33</v>
-      </c>
-      <c r="BB648" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC648" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD648" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE648" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF648" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG648" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH648" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI648" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ648" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK648" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL648">
         <v>1</v>
       </c>
@@ -103220,39 +99044,6 @@
       <c r="AY649">
         <v>24</v>
       </c>
-      <c r="BA649">
-        <v>34</v>
-      </c>
-      <c r="BB649" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC649" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD649" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BE649" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF649" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG649" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH649" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI649" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ649" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK649" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL649">
         <v>1</v>
       </c>
@@ -103378,39 +99169,6 @@
       <c r="AY650">
         <v>24</v>
       </c>
-      <c r="BA650">
-        <v>33</v>
-      </c>
-      <c r="BB650" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC650" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD650" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE650" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF650" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG650" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH650" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI650" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ650" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK650" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL650">
         <v>1</v>
       </c>
@@ -103536,39 +99294,6 @@
       <c r="AY651">
         <v>24</v>
       </c>
-      <c r="BA651">
-        <v>34</v>
-      </c>
-      <c r="BB651" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC651" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD651" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE651" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF651" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG651" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH651" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI651" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ651" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK651" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL651">
         <v>1</v>
       </c>
@@ -103694,39 +99419,6 @@
       <c r="AY652">
         <v>24</v>
       </c>
-      <c r="BA652">
-        <v>33</v>
-      </c>
-      <c r="BB652" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC652" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD652" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE652" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF652" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG652" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH652" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI652" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ652" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK652" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL652">
         <v>1</v>
       </c>
@@ -103852,39 +99544,6 @@
       <c r="AY653">
         <v>24</v>
       </c>
-      <c r="BA653">
-        <v>34</v>
-      </c>
-      <c r="BB653" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC653" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD653" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE653" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF653" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG653" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH653" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI653" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ653" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK653" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL653">
         <v>1</v>
       </c>
@@ -104010,39 +99669,6 @@
       <c r="AY654">
         <v>24</v>
       </c>
-      <c r="BA654">
-        <v>33</v>
-      </c>
-      <c r="BB654" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC654" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD654" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE654" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF654" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG654" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH654" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BI654" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ654" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK654" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL654">
         <v>1</v>
       </c>
@@ -104171,39 +99797,6 @@
       <c r="AY655">
         <v>24</v>
       </c>
-      <c r="BA655">
-        <v>33</v>
-      </c>
-      <c r="BB655" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC655" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD655" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE655" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BF655" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG655" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH655" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI655" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BJ655" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK655" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL655">
         <v>1</v>
       </c>
@@ -104329,39 +99922,6 @@
       <c r="AY656">
         <v>24</v>
       </c>
-      <c r="BA656">
-        <v>33</v>
-      </c>
-      <c r="BB656" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC656" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD656" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE656" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF656" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG656" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH656" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI656" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ656" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK656" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL656">
         <v>1</v>
       </c>
@@ -104487,39 +100047,6 @@
       <c r="AY657">
         <v>24</v>
       </c>
-      <c r="BA657">
-        <v>34</v>
-      </c>
-      <c r="BB657" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC657" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD657" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE657" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF657" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG657" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH657" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI657" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BJ657" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK657" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL657">
         <v>1</v>
       </c>
@@ -104645,39 +100172,6 @@
       <c r="AY658">
         <v>23</v>
       </c>
-      <c r="BA658">
-        <v>33</v>
-      </c>
-      <c r="BB658" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC658" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD658" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE658" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF658" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG658" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH658" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI658" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BJ658" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK658" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL658">
         <v>1</v>
       </c>
@@ -104803,39 +100297,6 @@
       <c r="AY659">
         <v>24</v>
       </c>
-      <c r="BA659">
-        <v>33</v>
-      </c>
-      <c r="BB659" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC659" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD659" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE659" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF659" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG659" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH659" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI659" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ659" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK659" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL659">
         <v>0</v>
       </c>
@@ -104961,39 +100422,6 @@
       <c r="AY660">
         <v>24</v>
       </c>
-      <c r="BA660">
-        <v>33</v>
-      </c>
-      <c r="BB660" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC660" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD660" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE660" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF660" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG660" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH660" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI660" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ660" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK660" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL660">
         <v>1</v>
       </c>
@@ -105119,36 +100547,6 @@
       <c r="AY661">
         <v>24</v>
       </c>
-      <c r="BA661">
-        <v>34</v>
-      </c>
-      <c r="BB661" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC661" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD661" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE661" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF661" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG661" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH661" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI661" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BK661" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL661">
         <v>1</v>
       </c>
@@ -105277,39 +100675,6 @@
       <c r="AY662">
         <v>23</v>
       </c>
-      <c r="BA662">
-        <v>33</v>
-      </c>
-      <c r="BB662" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC662" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD662" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE662" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF662" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG662" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH662" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI662" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ662" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK662" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL662">
         <v>1</v>
       </c>
@@ -105438,39 +100803,6 @@
       <c r="AY663">
         <v>24</v>
       </c>
-      <c r="BA663">
-        <v>33</v>
-      </c>
-      <c r="BB663" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC663" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD663" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE663" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF663" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG663" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH663" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI663" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ663" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK663" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL663">
         <v>1</v>
       </c>
@@ -105596,39 +100928,6 @@
       <c r="AY664">
         <v>24</v>
       </c>
-      <c r="BA664">
-        <v>44</v>
-      </c>
-      <c r="BB664" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC664" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD664" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE664" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF664" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG664" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH664" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI664" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ664" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK664" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL664">
         <v>1</v>
       </c>
@@ -105757,39 +101056,6 @@
       <c r="AY665">
         <v>24</v>
       </c>
-      <c r="BA665">
-        <v>34</v>
-      </c>
-      <c r="BB665" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC665" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD665" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE665" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF665" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG665" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH665" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI665" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ665" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK665" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL665">
         <v>1</v>
       </c>
@@ -105915,39 +101181,6 @@
       <c r="AY666">
         <v>9</v>
       </c>
-      <c r="BA666">
-        <v>33</v>
-      </c>
-      <c r="BB666" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC666" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD666" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE666" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF666" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG666" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH666" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI666" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ666" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK666" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL666">
         <v>0</v>
       </c>
@@ -106076,39 +101309,6 @@
       <c r="AY667">
         <v>22</v>
       </c>
-      <c r="BA667">
-        <v>23</v>
-      </c>
-      <c r="BB667" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC667" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD667" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE667" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF667" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG667" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH667" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI667" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ667" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK667" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL667">
         <v>1</v>
       </c>
@@ -106237,39 +101437,6 @@
       <c r="AY668">
         <v>21</v>
       </c>
-      <c r="BA668">
-        <v>23</v>
-      </c>
-      <c r="BB668" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC668" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD668" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE668" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF668" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG668" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH668" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI668" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ668" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK668" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL668">
         <v>1</v>
       </c>
@@ -106398,39 +101565,6 @@
       <c r="AY669">
         <v>24</v>
       </c>
-      <c r="BA669">
-        <v>34</v>
-      </c>
-      <c r="BB669" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC669" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD669" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE669" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF669" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG669" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH669" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI669" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ669" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK669" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL669">
         <v>1</v>
       </c>
@@ -106556,39 +101690,6 @@
       <c r="AY670">
         <v>24</v>
       </c>
-      <c r="BA670">
-        <v>33</v>
-      </c>
-      <c r="BB670" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC670" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD670" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE670" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF670" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG670" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH670" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BI670" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ670" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK670" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL670">
         <v>1</v>
       </c>
@@ -106714,39 +101815,6 @@
       <c r="AY671">
         <v>24</v>
       </c>
-      <c r="BA671">
-        <v>33</v>
-      </c>
-      <c r="BB671" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC671" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD671" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE671" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF671" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG671" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH671" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI671" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ671" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK671" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL671">
         <v>1</v>
       </c>
@@ -106806,39 +101874,6 @@
       <c r="AK672">
         <v>34</v>
       </c>
-      <c r="BA672">
-        <v>34</v>
-      </c>
-      <c r="BB672" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC672" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD672" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE672" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF672" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG672" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH672" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI672" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ672" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK672" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL672">
         <v>1</v>
       </c>
@@ -106967,39 +102002,6 @@
       <c r="AY673">
         <v>24</v>
       </c>
-      <c r="BA673">
-        <v>33</v>
-      </c>
-      <c r="BB673" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC673" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD673" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE673" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF673" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG673" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH673" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI673" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ673" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK673" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL673">
         <v>1</v>
       </c>
@@ -107128,39 +102130,6 @@
       <c r="AY674">
         <v>24</v>
       </c>
-      <c r="BA674">
-        <v>34</v>
-      </c>
-      <c r="BB674" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC674" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD674" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE674" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF674" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG674" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH674" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI674" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ674" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK674" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL674">
         <v>1</v>
       </c>
@@ -107289,39 +102258,6 @@
       <c r="AY675">
         <v>20</v>
       </c>
-      <c r="BA675">
-        <v>33</v>
-      </c>
-      <c r="BB675" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC675" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD675" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE675" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF675" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG675" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH675" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI675" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ675" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK675" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL675">
         <v>1</v>
       </c>
@@ -107450,39 +102386,6 @@
       <c r="AY676">
         <v>24</v>
       </c>
-      <c r="BA676">
-        <v>34</v>
-      </c>
-      <c r="BB676" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC676" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD676" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE676" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF676" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG676" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH676" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI676" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ676" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK676" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL676">
         <v>1</v>
       </c>
@@ -107611,39 +102514,6 @@
       <c r="AY677">
         <v>22</v>
       </c>
-      <c r="BA677">
-        <v>34</v>
-      </c>
-      <c r="BB677" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC677" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD677" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE677" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF677" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG677" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH677" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI677" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ677" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK677" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL677">
         <v>1</v>
       </c>
@@ -107897,39 +102767,6 @@
       <c r="AY679">
         <v>24</v>
       </c>
-      <c r="BA679">
-        <v>34</v>
-      </c>
-      <c r="BB679" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC679" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD679" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE679" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF679" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG679" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH679" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI679" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ679" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK679" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL679">
         <v>1</v>
       </c>
@@ -108058,39 +102895,6 @@
       <c r="AY680">
         <v>24</v>
       </c>
-      <c r="BA680">
-        <v>33</v>
-      </c>
-      <c r="BB680" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC680" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD680" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE680" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF680" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG680" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH680" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI680" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ680" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK680" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL680">
         <v>1</v>
       </c>
@@ -108219,39 +103023,6 @@
       <c r="AY681">
         <v>24</v>
       </c>
-      <c r="BA681">
-        <v>34</v>
-      </c>
-      <c r="BB681" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC681" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD681" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE681" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF681" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG681" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH681" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI681" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ681" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK681" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL681">
         <v>1</v>
       </c>
@@ -108380,39 +103151,6 @@
       <c r="AY682">
         <v>23</v>
       </c>
-      <c r="BA682">
-        <v>34</v>
-      </c>
-      <c r="BB682" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC682" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD682" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE682" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF682" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG682" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH682" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI682" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ682" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK682" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL682">
         <v>1</v>
       </c>
@@ -108538,39 +103276,6 @@
       <c r="AY683">
         <v>24</v>
       </c>
-      <c r="BA683">
-        <v>33</v>
-      </c>
-      <c r="BB683" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC683" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD683" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE683" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF683" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG683" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH683" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI683" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ683" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK683" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL683">
         <v>1</v>
       </c>
@@ -108699,39 +103404,6 @@
       <c r="AY684">
         <v>24</v>
       </c>
-      <c r="BA684">
-        <v>33</v>
-      </c>
-      <c r="BB684" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC684" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD684" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE684" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF684" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG684" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH684" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI684" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ684" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK684" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL684">
         <v>1</v>
       </c>
@@ -108860,39 +103532,6 @@
       <c r="AY685">
         <v>24</v>
       </c>
-      <c r="BA685">
-        <v>34</v>
-      </c>
-      <c r="BB685" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC685" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD685" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE685" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF685" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG685" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH685" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI685" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ685" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK685" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL685">
         <v>1</v>
       </c>
@@ -109021,39 +103660,6 @@
       <c r="AY686">
         <v>23</v>
       </c>
-      <c r="BA686">
-        <v>34</v>
-      </c>
-      <c r="BB686" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC686" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD686" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE686" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF686" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG686" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH686" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI686" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ686" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK686" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL686">
         <v>1</v>
       </c>
@@ -109182,39 +103788,6 @@
       <c r="AY687">
         <v>23</v>
       </c>
-      <c r="BA687">
-        <v>33</v>
-      </c>
-      <c r="BB687" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC687" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD687" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE687" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF687" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG687" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH687" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI687" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BJ687" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK687" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL687">
         <v>1</v>
       </c>
@@ -109340,39 +103913,6 @@
       <c r="AY688">
         <v>24</v>
       </c>
-      <c r="BA688">
-        <v>33</v>
-      </c>
-      <c r="BB688" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC688" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD688" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE688" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF688" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG688" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH688" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI688" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ688" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK688" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL688">
         <v>1</v>
       </c>
@@ -109495,39 +104035,6 @@
       <c r="AY689">
         <v>24</v>
       </c>
-      <c r="BA689">
-        <v>33</v>
-      </c>
-      <c r="BB689" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC689" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD689" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE689" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF689" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG689" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH689" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI689" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ689" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK689" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL689">
         <v>1</v>
       </c>
@@ -109656,39 +104163,6 @@
       <c r="AY690">
         <v>23</v>
       </c>
-      <c r="BA690">
-        <v>34</v>
-      </c>
-      <c r="BB690" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC690" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD690" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE690" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF690" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG690" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH690" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI690" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ690" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK690" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL690">
         <v>1</v>
       </c>
@@ -109817,39 +104291,6 @@
       <c r="AY691">
         <v>20</v>
       </c>
-      <c r="BA691">
-        <v>33</v>
-      </c>
-      <c r="BB691" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC691" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD691" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE691" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF691" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG691" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH691" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI691" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ691" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK691" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL691">
         <v>1</v>
       </c>
@@ -109978,39 +104419,6 @@
       <c r="AY692">
         <v>24</v>
       </c>
-      <c r="BA692">
-        <v>34</v>
-      </c>
-      <c r="BB692" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC692" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD692" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE692" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF692" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG692" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH692" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI692" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ692" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK692" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL692">
         <v>1</v>
       </c>
@@ -110139,39 +104547,6 @@
       <c r="AY693">
         <v>23</v>
       </c>
-      <c r="BA693">
-        <v>33</v>
-      </c>
-      <c r="BB693" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC693" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD693" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE693" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF693" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG693" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH693" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI693" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ693" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK693" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL693">
         <v>1</v>
       </c>
@@ -110297,39 +104672,6 @@
       <c r="AY694">
         <v>24</v>
       </c>
-      <c r="BA694">
-        <v>24</v>
-      </c>
-      <c r="BB694" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC694" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD694" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BE694" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF694" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG694" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH694" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI694" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ694" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK694" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL694">
         <v>1</v>
       </c>
@@ -110458,39 +104800,6 @@
       <c r="AY695">
         <v>22</v>
       </c>
-      <c r="BA695">
-        <v>34</v>
-      </c>
-      <c r="BB695" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC695" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD695" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE695" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF695" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG695" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH695" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI695" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ695" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK695" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL695">
         <v>1</v>
       </c>
@@ -110788,39 +105097,6 @@
       <c r="L698">
         <v>5</v>
       </c>
-      <c r="BA698">
-        <v>34</v>
-      </c>
-      <c r="BB698" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC698" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD698" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE698" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF698" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG698" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH698" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI698" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ698" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK698" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL698">
         <v>1</v>
       </c>
@@ -110949,39 +105225,6 @@
       <c r="AY699">
         <v>24</v>
       </c>
-      <c r="BA699">
-        <v>33</v>
-      </c>
-      <c r="BB699" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC699" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD699" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE699" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF699" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG699" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH699" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI699" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BJ699" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK699" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL699">
         <v>1</v>
       </c>
@@ -111107,39 +105350,6 @@
       <c r="AY700">
         <v>24</v>
       </c>
-      <c r="BA700">
-        <v>33</v>
-      </c>
-      <c r="BB700" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC700" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD700" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE700" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF700" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG700" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH700" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI700" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ700" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK700" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL700">
         <v>1</v>
       </c>
@@ -111184,39 +105394,6 @@
       <c r="AD701">
         <v>28</v>
       </c>
-      <c r="BA701">
-        <v>33</v>
-      </c>
-      <c r="BB701" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC701" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD701" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE701" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF701" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG701" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH701" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI701" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BJ701" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK701" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL701">
         <v>1</v>
       </c>
@@ -111342,39 +105519,6 @@
       <c r="AY702">
         <v>23</v>
       </c>
-      <c r="BA702">
-        <v>33</v>
-      </c>
-      <c r="BB702" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC702" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD702" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE702" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF702" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG702" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH702" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI702" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ702" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK702" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL702">
         <v>1</v>
       </c>
@@ -111503,39 +105647,6 @@
       <c r="AY703">
         <v>23</v>
       </c>
-      <c r="BA703">
-        <v>33</v>
-      </c>
-      <c r="BB703" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC703" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD703" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE703" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF703" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG703" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH703" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI703" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ703" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK703" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL703">
         <v>1</v>
       </c>
@@ -111664,39 +105775,6 @@
       <c r="AY704">
         <v>24</v>
       </c>
-      <c r="BA704">
-        <v>33</v>
-      </c>
-      <c r="BB704" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC704" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD704" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE704" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF704" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG704" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH704" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI704" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ704" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK704" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL704">
         <v>1</v>
       </c>
@@ -111825,39 +105903,6 @@
       <c r="AY705">
         <v>24</v>
       </c>
-      <c r="BA705">
-        <v>33</v>
-      </c>
-      <c r="BB705" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC705" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD705" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE705" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF705" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG705" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH705" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI705" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ705" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK705" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL705">
         <v>1</v>
       </c>
@@ -111986,39 +106031,6 @@
       <c r="AY706">
         <v>24</v>
       </c>
-      <c r="BA706">
-        <v>33</v>
-      </c>
-      <c r="BB706" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC706" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD706" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE706" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF706" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG706" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH706" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI706" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ706" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK706" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL706">
         <v>1</v>
       </c>
@@ -112147,39 +106159,6 @@
       <c r="AY707">
         <v>24</v>
       </c>
-      <c r="BA707">
-        <v>33</v>
-      </c>
-      <c r="BB707" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC707" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD707" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE707" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF707" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG707" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH707" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI707" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BJ707" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK707" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL707">
         <v>1</v>
       </c>
@@ -112308,39 +106287,6 @@
       <c r="AY708">
         <v>24</v>
       </c>
-      <c r="BA708">
-        <v>33</v>
-      </c>
-      <c r="BB708" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC708" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD708" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE708" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF708" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG708" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH708" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI708" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BJ708" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK708" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL708">
         <v>1</v>
       </c>
@@ -112466,39 +106412,6 @@
       <c r="AY709">
         <v>24</v>
       </c>
-      <c r="BA709">
-        <v>33</v>
-      </c>
-      <c r="BB709" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC709" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD709" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE709" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF709" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG709" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH709" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI709" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ709" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK709" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL709">
         <v>0</v>
       </c>
@@ -112627,39 +106540,6 @@
       <c r="AY710">
         <v>23</v>
       </c>
-      <c r="BA710">
-        <v>33</v>
-      </c>
-      <c r="BB710" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC710" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD710" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE710" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF710" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG710" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH710" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI710" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ710" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK710" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL710">
         <v>1</v>
       </c>
@@ -112701,39 +106581,6 @@
       <c r="L711">
         <v>5</v>
       </c>
-      <c r="BA711">
-        <v>33</v>
-      </c>
-      <c r="BB711" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC711" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD711" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE711" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF711" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG711" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH711" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI711" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ711" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK711" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL711">
         <v>1</v>
       </c>
@@ -113150,39 +106997,6 @@
       <c r="AY715">
         <v>24</v>
       </c>
-      <c r="BA715">
-        <v>33</v>
-      </c>
-      <c r="BB715" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC715" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD715" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE715" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF715" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG715" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH715" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI715" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ715" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK715" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL715">
         <v>1</v>
       </c>
@@ -113311,39 +107125,6 @@
       <c r="AY716">
         <v>24</v>
       </c>
-      <c r="BA716">
-        <v>23</v>
-      </c>
-      <c r="BB716" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC716" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD716" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE716" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF716" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG716" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH716" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI716" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ716" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK716" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL716">
         <v>1</v>
       </c>
@@ -113472,39 +107253,6 @@
       <c r="AY717">
         <v>19</v>
       </c>
-      <c r="BA717">
-        <v>33</v>
-      </c>
-      <c r="BB717" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC717" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD717" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE717" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF717" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG717" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH717" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI717" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ717" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK717" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL717">
         <v>1</v>
       </c>
@@ -113630,39 +107378,6 @@
       <c r="AY718">
         <v>24</v>
       </c>
-      <c r="BA718">
-        <v>33</v>
-      </c>
-      <c r="BB718" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC718" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD718" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE718" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF718" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG718" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH718" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI718" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ718" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK718" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL718">
         <v>1</v>
       </c>
@@ -113704,39 +107419,6 @@
       <c r="L719">
         <v>5</v>
       </c>
-      <c r="BA719">
-        <v>33</v>
-      </c>
-      <c r="BB719" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC719" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD719" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE719" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF719" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG719" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH719" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI719" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ719" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK719" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL719">
         <v>1</v>
       </c>
@@ -113859,39 +107541,6 @@
       <c r="AY720">
         <v>24</v>
       </c>
-      <c r="BA720">
-        <v>33</v>
-      </c>
-      <c r="BB720" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC720" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD720" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE720" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF720" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG720" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH720" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI720" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ720" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK720" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL720">
         <v>1</v>
       </c>
@@ -114145,39 +107794,6 @@
       <c r="AY722">
         <v>24</v>
       </c>
-      <c r="BA722">
-        <v>33</v>
-      </c>
-      <c r="BB722" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC722" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD722" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE722" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF722" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG722" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH722" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI722" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ722" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK722" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL722">
         <v>1</v>
       </c>
@@ -114306,39 +107922,6 @@
       <c r="AY723">
         <v>24</v>
       </c>
-      <c r="BA723">
-        <v>33</v>
-      </c>
-      <c r="BB723" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC723" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD723" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE723" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF723" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG723" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH723" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI723" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ723" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK723" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL723">
         <v>1</v>
       </c>
@@ -114592,39 +108175,6 @@
       <c r="AY725">
         <v>24</v>
       </c>
-      <c r="BA725">
-        <v>34</v>
-      </c>
-      <c r="BB725" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC725" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD725" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE725" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF725" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG725" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH725" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI725" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ725" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK725" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL725">
         <v>1</v>
       </c>
@@ -114750,39 +108300,6 @@
       <c r="AY726">
         <v>19</v>
       </c>
-      <c r="BA726">
-        <v>33</v>
-      </c>
-      <c r="BB726" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC726" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD726" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE726" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF726" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG726" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH726" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI726" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ726" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK726" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL726">
         <v>1</v>
       </c>
@@ -114952,39 +108469,6 @@
       <c r="L728">
         <v>5</v>
       </c>
-      <c r="BA728">
-        <v>33</v>
-      </c>
-      <c r="BB728" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC728" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD728" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE728" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF728" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG728" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH728" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI728" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ728" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK728" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL728">
         <v>1</v>
       </c>
@@ -115026,39 +108510,6 @@
       <c r="L729">
         <v>5</v>
       </c>
-      <c r="BA729">
-        <v>33</v>
-      </c>
-      <c r="BB729" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC729" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD729" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE729" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF729" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG729" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH729" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI729" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ729" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK729" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL729">
         <v>1</v>
       </c>
@@ -115100,39 +108551,6 @@
       <c r="L730">
         <v>5</v>
       </c>
-      <c r="BA730">
-        <v>44</v>
-      </c>
-      <c r="BB730" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC730" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD730" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE730" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF730" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG730" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH730" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI730" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ730" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK730" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL730">
         <v>1</v>
       </c>
@@ -115162,39 +108580,6 @@
       <c r="L731">
         <v>5</v>
       </c>
-      <c r="BA731">
-        <v>23</v>
-      </c>
-      <c r="BB731" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC731" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD731" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE731" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF731" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG731" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH731" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI731" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ731" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK731" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL731">
         <v>0</v>
       </c>
@@ -115343,39 +108728,6 @@
       <c r="AY733">
         <v>24</v>
       </c>
-      <c r="BA733">
-        <v>34</v>
-      </c>
-      <c r="BB733" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC733" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD733" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE733" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF733" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG733" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH733" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI733" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ733" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK733" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL733">
         <v>0</v>
       </c>
@@ -115408,39 +108760,6 @@
       <c r="L734">
         <v>5</v>
       </c>
-      <c r="BA734">
-        <v>33</v>
-      </c>
-      <c r="BB734" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC734" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD734" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE734" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF734" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG734" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH734" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI734" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ734" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK734" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL734">
         <v>0</v>
       </c>
@@ -115560,39 +108879,6 @@
       <c r="AY735">
         <v>24</v>
       </c>
-      <c r="BA735">
-        <v>44</v>
-      </c>
-      <c r="BB735" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC735" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD735" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE735" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF735" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG735" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH735" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI735" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ735" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK735" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL735">
         <v>0</v>
       </c>
@@ -115764,39 +109050,6 @@
       <c r="L738">
         <v>5</v>
       </c>
-      <c r="BA738">
-        <v>33</v>
-      </c>
-      <c r="BB738" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC738" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD738" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE738" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF738" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG738" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH738" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI738" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ738" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK738" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL738">
         <v>0</v>
       </c>
@@ -115826,39 +109079,6 @@
       <c r="L739">
         <v>5</v>
       </c>
-      <c r="BA739">
-        <v>33</v>
-      </c>
-      <c r="BB739" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC739" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD739" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE739" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF739" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG739" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH739" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI739" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ739" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK739" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL739">
         <v>0</v>
       </c>
@@ -115888,39 +109108,6 @@
       <c r="L740">
         <v>5</v>
       </c>
-      <c r="BA740">
-        <v>33</v>
-      </c>
-      <c r="BB740" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC740" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD740" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE740" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF740" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG740" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH740" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI740" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ740" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK740" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL740">
         <v>0</v>
       </c>
@@ -116084,39 +109271,6 @@
       <c r="AB742">
         <v>10</v>
       </c>
-      <c r="BA742">
-        <v>44</v>
-      </c>
-      <c r="BB742" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC742" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD742" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE742" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF742" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG742" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH742" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI742" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ742" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK742" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL742">
         <v>0</v>
       </c>
@@ -116161,39 +109315,6 @@
       <c r="AB743">
         <v>12</v>
       </c>
-      <c r="BA743">
-        <v>33</v>
-      </c>
-      <c r="BB743" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC743" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD743" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE743" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF743" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG743" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH743" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI743" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ743" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK743" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL743">
         <v>0</v>
       </c>
@@ -116316,39 +109437,6 @@
       <c r="AY744">
         <v>24</v>
       </c>
-      <c r="BA744">
-        <v>23</v>
-      </c>
-      <c r="BB744" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC744" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD744" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE744" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF744" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG744" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH744" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI744" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ744" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK744" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL744">
         <v>0</v>
       </c>
@@ -116471,39 +109559,6 @@
       <c r="AY745">
         <v>24</v>
       </c>
-      <c r="BA745">
-        <v>33</v>
-      </c>
-      <c r="BB745" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC745" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD745" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE745" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF745" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG745" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH745" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI745" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ745" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK745" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL745">
         <v>0</v>
       </c>
@@ -116626,39 +109681,6 @@
       <c r="AY746">
         <v>24</v>
       </c>
-      <c r="BA746">
-        <v>33</v>
-      </c>
-      <c r="BB746" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC746" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD746" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE746" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF746" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG746" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH746" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI746" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ746" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK746" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL746">
         <v>0</v>
       </c>
@@ -116781,39 +109803,6 @@
       <c r="AY747">
         <v>24</v>
       </c>
-      <c r="BA747">
-        <v>34</v>
-      </c>
-      <c r="BB747" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC747" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD747" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE747" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF747" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG747" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH747" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI747" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ747" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK747" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL747">
         <v>0</v>
       </c>
@@ -116936,39 +109925,6 @@
       <c r="AY748">
         <v>24</v>
       </c>
-      <c r="BA748">
-        <v>34</v>
-      </c>
-      <c r="BB748" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC748" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD748" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE748" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF748" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG748" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH748" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI748" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ748" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK748" t="s">
-        <v>1490</v>
-      </c>
       <c r="BL748">
         <v>0</v>
       </c>
@@ -117091,39 +110047,6 @@
       <c r="AY749">
         <v>22</v>
       </c>
-      <c r="BA749">
-        <v>33</v>
-      </c>
-      <c r="BB749" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC749" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD749" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE749" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF749" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BG749" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH749" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI749" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ749" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK749" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL749">
         <v>0</v>
       </c>
@@ -117162,39 +110085,6 @@
       <c r="AB750">
         <v>13</v>
       </c>
-      <c r="BA750">
-        <v>33</v>
-      </c>
-      <c r="BB750" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC750" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD750" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE750" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF750" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG750" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH750" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI750" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ750" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK750" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL750">
         <v>0</v>
       </c>
@@ -117233,39 +110123,6 @@
       <c r="AB751">
         <v>6</v>
       </c>
-      <c r="BA751">
-        <v>34</v>
-      </c>
-      <c r="BB751" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC751" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD751" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE751" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF751" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG751" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH751" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI751" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ751" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK751" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL751">
         <v>0</v>
       </c>
@@ -117292,39 +110149,6 @@
       <c r="L752">
         <v>5</v>
       </c>
-      <c r="BA752">
-        <v>33</v>
-      </c>
-      <c r="BB752" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC752" t="s">
-        <v>1492</v>
-      </c>
-      <c r="BD752" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE752" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BF752" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG752" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BH752" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI752" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BJ752" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK752" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL752">
         <v>0</v>
       </c>
@@ -117447,39 +110271,6 @@
       <c r="AY753">
         <v>23</v>
       </c>
-      <c r="BA753">
-        <v>33</v>
-      </c>
-      <c r="BB753" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BC753" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BD753" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BE753" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF753" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG753" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH753" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI753" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ753" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BK753" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL753">
         <v>0</v>
       </c>
@@ -117599,39 +110390,6 @@
       <c r="AY754">
         <v>22</v>
       </c>
-      <c r="BA754">
-        <v>34</v>
-      </c>
-      <c r="BB754" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BC754" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD754" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BE754" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF754" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BG754" t="s">
-        <v>1498</v>
-      </c>
-      <c r="BH754" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BI754" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ754" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BK754" t="s">
-        <v>1488</v>
-      </c>
       <c r="BL754">
         <v>0</v>
       </c>
@@ -117748,39 +110506,6 @@
       <c r="AY755">
         <v>24</v>
       </c>
-      <c r="BA755">
-        <v>34</v>
-      </c>
-      <c r="BB755" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BC755" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BD755" t="s">
-        <v>1490</v>
-      </c>
-      <c r="BE755" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BF755" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BG755" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BH755" t="s">
-        <v>1496</v>
-      </c>
-      <c r="BI755" t="s">
-        <v>1489</v>
-      </c>
-      <c r="BJ755" t="s">
-        <v>1495</v>
-      </c>
-      <c r="BK755" t="s">
-        <v>1489</v>
-      </c>
       <c r="BL755">
         <v>0</v>
       </c>
@@ -117806,9 +110531,6 @@
       </c>
       <c r="L756">
         <v>5</v>
-      </c>
-      <c r="BA756">
-        <v>22</v>
       </c>
       <c r="BL756">
         <v>0</v>

--- a/data/participants_megtusalen.xlsx
+++ b/data/participants_megtusalen.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cristina\repos\megtusalen_validation2026\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROGRAMMING\MATLAB\MEGTUSALEN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E5D3F2-39A8-473F-A8B2-78389B326F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080D33F9-8F8E-41BD-96E1-D19D1CF72420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A8CE7551-8922-47F6-B549-E6B85DA15C6C}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{A8CE7551-8922-47F6-B549-E6B85DA15C6C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$BS$730</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$BS$761</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4856,7 +4856,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -5173,7 +5173,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FAB02E2-8283-44DB-BC1E-88DE8C1F843E}">
   <dimension ref="A1:BS761"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
@@ -111472,9 +111472,6 @@
       <c r="B731" t="s">
         <v>1511</v>
       </c>
-      <c r="E731">
-        <v>1</v>
-      </c>
       <c r="BP731">
         <v>0</v>
       </c>
@@ -111904,9 +111901,6 @@
       <c r="B737" t="s">
         <v>1517</v>
       </c>
-      <c r="E737">
-        <v>1</v>
-      </c>
       <c r="BP737">
         <v>0</v>
       </c>
@@ -112941,9 +112935,6 @@
       <c r="B750" t="s">
         <v>1530</v>
       </c>
-      <c r="E750">
-        <v>1</v>
-      </c>
       <c r="AC750">
         <v>48</v>
       </c>
@@ -112973,9 +112964,6 @@
       <c r="B751" t="s">
         <v>1531</v>
       </c>
-      <c r="E751">
-        <v>1</v>
-      </c>
       <c r="AC751">
         <v>24</v>
       </c>
@@ -113005,9 +112993,6 @@
       <c r="B752" t="s">
         <v>1532</v>
       </c>
-      <c r="E752">
-        <v>1</v>
-      </c>
       <c r="BP752">
         <v>0</v>
       </c>
@@ -113391,9 +113376,6 @@
       <c r="B756" t="s">
         <v>1567</v>
       </c>
-      <c r="E756">
-        <v>1</v>
-      </c>
       <c r="BP756">
         <v>0</v>
       </c>
@@ -113505,6 +113487,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:BS761" xr:uid="{0FAB02E2-8283-44DB-BC1E-88DE8C1F843E}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
